--- a/assets/constructions/examples/ctd_jse_hand_each.xlsx
+++ b/assets/constructions/examples/ctd_jse_hand_each.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,32 +654,57 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TAP 5/8 WHT. ROUGH - A 4</t>
+          <t>N1110-3 UNC5/16-18 2B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>DC SWISS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A4 ROUGHING</t>
+          <t>N1110-3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PKN</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WH55</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -689,20 +714,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.875</v>
+        <v>0.313</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>5/16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 5/8"</t>
+          <t>5/16" - 18 UNC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -711,42 +736,40 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.411</v>
+      </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>12</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>h9</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="W2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="X2" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -755,7 +778,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:12X9</t>
+          <t>DCON_X_DRVS:8x6.3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,23 +786,31 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>HSS</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+          <t>PME</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>HS</t>
@@ -797,7 +828,7 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>DIN 2184-2</t>
+          <t>ISO 529</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr"/>
@@ -812,24 +843,35 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2022 / Vergnano-Thread-Mills</t>
+          <t>2020 / DC Swiss website</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TAP 7/16-20 UNF ROUGH - A 8</t>
+          <t>T101MF8×0,75</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>АКСИС</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A8 ROUGHING</t>
+          <t>T10MF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -840,7 +882,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -850,20 +892,20 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>11.113</v>
+        <v>8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7/16" - 20 UNF</t>
+          <t>M8x0.75</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -878,22 +920,22 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>20</v>
-      </c>
+        <v>7.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -901,11 +943,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -914,7 +956,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:8X6.2</t>
+          <t>DCON_X_DRVS:6x4.9</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -924,21 +966,27 @@
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>HSS</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>HS</t>
@@ -956,7 +1004,7 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>DIN 2184-2</t>
+          <t>DIN 2181</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr"/>
@@ -971,24 +1019,35 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2022 / Vergnano-Thread-Mills</t>
+          <t>2026 / АКСИС Металлорежущий инструмент</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TAP M 16x1 ROUGH - A 2</t>
+          <t>T7109749 #2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A2ROUGHING</t>
+          <t>T7109</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1004,67 +1063,65 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>M16x1</t>
+          <t>M22x2.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>II</t>
         </is>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>h9</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>22</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>62</v>
+      </c>
       <c r="X4" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1073,7 +1130,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:12X9</t>
+          <t>DCON_X_DRVS:18x14.5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1085,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1094,14 +1151,10 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>HSSE</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>HSSE</t>
-        </is>
-      </c>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>HSS</t>
@@ -1127,7 +1180,7 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>DIN 2181</t>
+          <t>DIN 352</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr"/>
@@ -1142,134 +1195,145 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2020 / Vergnano Catalog</t>
+          <t>2025 / YG1 Нарезание резьбы</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N410-3 M34x1.5 6H</t>
+          <t>T7363D29 #2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DC SWISS</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N410-3</t>
+          <t>T7363</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMKN</t>
+          <t>PKN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6H</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>2"</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>M34x1,5</t>
+          <t>2" - 4 UNC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>45.25</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>II</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
+        <v>65</v>
+      </c>
+      <c r="W5" t="n">
+        <v>102</v>
+      </c>
+      <c r="X5" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>DCON_X_DRVS:40x32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
         <v>32</v>
       </c>
-      <c r="W5" t="n">
-        <v>32</v>
-      </c>
-      <c r="X5" t="n">
-        <v>170</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>DCON_X_DRVS:28X22</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>WORKPIECE</t>
-        </is>
-      </c>
-      <c r="AB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>22</v>
-      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AH5" t="n">
@@ -1292,7 +1356,7 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>DIN 376</t>
+          <t>DIN 351</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr"/>
@@ -1307,24 +1371,35 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2020 / DC Swiss website</t>
+          <t>2025 / YG1 Нарезание резьбы</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TAP M 3,5x0,6 FIN - A 1</t>
+          <t>T7363209 #1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A1FINISHING</t>
+          <t>T7363</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1335,7 +1410,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1345,20 +1420,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6H / ISO 2</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>0.125</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>M3,5</t>
+          <t>#5 - 40 UNC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1367,42 +1442,38 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>40</v>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>h9</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X6" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1411,7 +1482,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:4X3</t>
+          <t>DCON_X_DRVS:3.5x2.7</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1423,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1435,11 +1506,7 @@
           <t>HSS</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>HSS</t>
-        </is>
-      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>HSS</t>
@@ -1465,7 +1532,7 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>DIN 352</t>
+          <t>DIN 351</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr"/>
@@ -1480,7 +1547,18 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2020 / Vergnano Catalog</t>
+          <t>2025 / YG1 Нарезание резьбы</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>PKN</t>
         </is>
       </c>
     </row>
